--- a/pipeline_eval/eval_results/overall_metrics_report_approach1.xlsx
+++ b/pipeline_eval/eval_results/overall_metrics_report_approach1.xlsx
@@ -416,29 +416,6 @@
   </sheetPr>
   <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="31" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="29" customWidth="1" min="10" max="10"/>
-    <col width="29" customWidth="1" min="11" max="11"/>
-    <col width="29" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="31" customWidth="1" min="14" max="14"/>
-    <col width="31" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="29" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
-    <col width="29" customWidth="1" min="20" max="20"/>
-    <col width="29" customWidth="1" min="21" max="21"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -549,67 +526,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>1683</v>
+        <v>1986</v>
       </c>
       <c r="C2" t="n">
-        <v>800</v>
+        <v>1217</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5957813428401664</v>
+        <v>0.5778</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7641711229946524</v>
+        <v>0.7027</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8336898395721926</v>
+        <v>0.836</v>
       </c>
       <c r="G2" t="n">
-        <v>0.47534165181224</v>
+        <v>0.6891</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5688888888888888</v>
+        <v>0.8455</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6001346801346802</v>
+        <v>0.7931</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3080898876404494</v>
+        <v>0.6956</v>
       </c>
       <c r="K2" t="n">
-        <v>0.601919770773639</v>
+        <v>0.7372</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1724495677233429</v>
+        <v>0.3719</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5953777777777778</v>
+        <v>0.5775816515609264</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7646777777777778</v>
+        <v>0.7016392648539778</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8331222222222222</v>
+        <v>0.8362348640483382</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4914666666666667</v>
+        <v>0.6982272507552871</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5764717099797745</v>
+        <v>0.8445998343693037</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6171558985856372</v>
+        <v>0.8001398652907165</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2723154623154624</v>
+        <v>0.6761796629571302</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6229787589578193</v>
+        <v>0.7459767221333794</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1766227711813825</v>
+        <v>0.3771689315568572</v>
       </c>
     </row>
   </sheetData>
@@ -623,26 +600,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -739,43 +698,43 @@
         <v>199</v>
       </c>
       <c r="D2" t="n">
-        <v>120.9</v>
+        <v>115.9</v>
       </c>
       <c r="E2" t="n">
-        <v>154.5</v>
+        <v>141.4</v>
       </c>
       <c r="F2" t="n">
-        <v>166.6</v>
+        <v>166</v>
       </c>
       <c r="G2" t="n">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6074999999999999</v>
+        <v>0.5821716515609264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7766</v>
+        <v>0.7103592648539778</v>
       </c>
       <c r="J2" t="n">
-        <v>0.837</v>
+        <v>0.8341448640483383</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3976999999999999</v>
+        <v>0.6140072507552871</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5237499999999999</v>
+        <v>0.8040913960566604</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7308108108108109</v>
+        <v>0.9183391026692107</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1646153846153846</v>
+        <v>0.5949103429321769</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6157142857142857</v>
+        <v>0.7359153217894078</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.04567633263039111</v>
       </c>
     </row>
     <row r="3">
@@ -791,43 +750,43 @@
         <v>105</v>
       </c>
       <c r="D3" t="n">
-        <v>68.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>82.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="G3" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6528999999999999</v>
+        <v>0.6275716515609264</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7898999999999999</v>
+        <v>0.7236592648539778</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8721</v>
+        <v>0.8692448640483383</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6314</v>
+        <v>0.8477072507552871</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7481818181818183</v>
+        <v>0.9298</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8430769230769232</v>
+        <v>0.9430000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.2102949583167922</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7481818181818183</v>
+        <v>0.8683828542569403</v>
       </c>
       <c r="P3" t="n">
-        <v>0.22</v>
+        <v>0.4392933539069868</v>
       </c>
     </row>
     <row r="4">
@@ -843,43 +802,43 @@
         <v>193</v>
       </c>
       <c r="D4" t="n">
-        <v>116</v>
+        <v>111.1</v>
       </c>
       <c r="E4" t="n">
-        <v>147.1</v>
+        <v>134.4</v>
       </c>
       <c r="F4" t="n">
-        <v>162.7</v>
+        <v>162.1</v>
       </c>
       <c r="G4" t="n">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6009</v>
+        <v>0.5755716515609265</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7624</v>
+        <v>0.6961592648539778</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8428</v>
+        <v>0.8399448640483383</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.7551072507552871</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5429032258064517</v>
+        <v>0.823244621863112</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6607407407407407</v>
+        <v>0.8482690325991405</v>
       </c>
       <c r="N4" t="n">
-        <v>0.53</v>
+        <v>0.9081999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7090697674418605</v>
+        <v>0.8292708035169826</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1834146341463415</v>
+        <v>0.4027079880533283</v>
       </c>
     </row>
     <row r="5">
@@ -895,43 +854,43 @@
         <v>260</v>
       </c>
       <c r="D5" t="n">
-        <v>154.5</v>
+        <v>148</v>
       </c>
       <c r="E5" t="n">
-        <v>193.8</v>
+        <v>176.6</v>
       </c>
       <c r="F5" t="n">
-        <v>212.8</v>
+        <v>212</v>
       </c>
       <c r="G5" t="n">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5943999999999999</v>
+        <v>0.5690716515609264</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7454</v>
+        <v>0.6791592648539778</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8182999999999999</v>
+        <v>0.8154448640483383</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5254</v>
+        <v>0.7417072507552871</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6597297297297298</v>
+        <v>0.9298</v>
       </c>
       <c r="M5" t="n">
-        <v>0.745</v>
+        <v>0.9325282918583998</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3254545454545454</v>
+        <v>0.7557495037713378</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6417117117117117</v>
+        <v>0.7619127477868337</v>
       </c>
       <c r="P5" t="n">
-        <v>0.179016393442623</v>
+        <v>0.3983097473496098</v>
       </c>
     </row>
     <row r="6">
@@ -944,254 +903,306 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>97</v>
+        <v>242</v>
       </c>
       <c r="D6" t="n">
-        <v>50.1</v>
+        <v>160</v>
       </c>
       <c r="E6" t="n">
-        <v>71.40000000000001</v>
+        <v>185.8</v>
       </c>
       <c r="F6" t="n">
-        <v>75.90000000000001</v>
+        <v>213.1</v>
       </c>
       <c r="G6" t="n">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5164</v>
+        <v>0.6610716515609264</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7359</v>
+        <v>0.7678592648539778</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7826</v>
+        <v>0.8807448640483383</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6837072507552872</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6074193548387097</v>
+        <v>0.88776075089537</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7661538461538462</v>
+        <v>0.9430000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3514285714285714</v>
+        <v>0.7817235297453637</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7376923076923076</v>
+        <v>0.7885187930844678</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.2049183539069868</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>eval_conv_6.xlsx</t>
+          <t>eval_conv_5.xlsx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="D7" t="n">
-        <v>134.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>163.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>174.4</v>
+        <v>124.7</v>
       </c>
       <c r="G7" t="n">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7063999999999999</v>
+        <v>0.4753716515609264</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8622</v>
+        <v>0.6322592648539779</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.7889448640483383</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4126</v>
+        <v>0.7472072507552872</v>
       </c>
       <c r="L7" t="n">
-        <v>0.43</v>
+        <v>0.8436747293899937</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3317647058823529</v>
+        <v>0.8575282918583998</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5492307692307693</v>
+        <v>0.7817235297453637</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5083132530120482</v>
+        <v>0.8405236167202833</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2949999999999999</v>
+        <v>0.3964362110498438</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>eval_conv_7.xlsx</t>
+          <t>eval_conv_6.xlsx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>239</v>
+        <v>190</v>
       </c>
       <c r="D8" t="n">
-        <v>137</v>
+        <v>129.4</v>
       </c>
       <c r="E8" t="n">
-        <v>187.2</v>
+        <v>151.2</v>
       </c>
       <c r="F8" t="n">
-        <v>205.4</v>
+        <v>173.8</v>
       </c>
       <c r="G8" t="n">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5731999999999999</v>
+        <v>0.6810716515609264</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7834</v>
+        <v>0.7959592648539778</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8595999999999999</v>
+        <v>0.9149448640483383</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3663</v>
+        <v>0.6289072507552871</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5966666666666667</v>
+        <v>0.7103413960566604</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2533333333333333</v>
+        <v>0.5192929977407528</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.9081999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.489322033898305</v>
+        <v>0.6285142890871702</v>
       </c>
       <c r="P8" t="n">
-        <v>0.22</v>
+        <v>0.5142933539069867</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eval_conv_8.xlsx</t>
+          <t>eval_conv_7.xlsx</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>106.5</v>
+        <v>130.9</v>
       </c>
       <c r="E9" t="n">
-        <v>135.8</v>
+        <v>171.4</v>
       </c>
       <c r="F9" t="n">
-        <v>151.9</v>
+        <v>204.8</v>
       </c>
       <c r="G9" t="n">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5436</v>
+        <v>0.5478716515609264</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6930999999999999</v>
+        <v>0.7171592648539779</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7748999999999999</v>
+        <v>0.8567448640483383</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4416</v>
+        <v>0.5826072507552871</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5245945945945947</v>
+        <v>0.877008062723327</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6472727272727273</v>
+        <v>0.4408616251917332</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2415384615384616</v>
+        <v>0.5102949583167923</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5601369863013699</v>
+        <v>0.6095230699734271</v>
       </c>
       <c r="P9" t="n">
-        <v>0.12</v>
+        <v>0.4392933539069868</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>eval_conv_8.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>196</v>
+      </c>
+      <c r="D10" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>129</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5182716515609265</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6268592648539778</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7720448640483383</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6579072507552871</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.804935990651255</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.8348010191311271</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.6718334198552539</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.6803380223764919</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.3392933539069869</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>eval_conv_9.xlsx</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>204</v>
       </c>
-      <c r="D10" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="E10" t="n">
-        <v>149.6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>161.8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>103</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.5630999999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.7332</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.7929999999999999</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.5071</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.5549999999999999</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.57625</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.2085714285714285</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.5966666666666667</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.3721739130434782</v>
+      <c r="D11" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>136.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>148</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5377716515609264</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6669592648539778</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7901448640483383</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7234072507552871</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8353413960566604</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.7637782918583998</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.6388663868882207</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.7168677027417887</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.591467266950465</v>
       </c>
     </row>
   </sheetData>
